--- a/Claude outputs/AI_Calculator_Shopping_List.xlsx
+++ b/Claude outputs/AI_Calculator_Shopping_List.xlsx
@@ -1795,7 +1795,7 @@
       </c>
       <c r="P31" s="17" t="inlineStr">
         <is>
-          <t>Legs straightened into J3. Meter-check against the cable before gluing.</t>
+          <t>Legs straightened into J3. Meter-check against the cable before gluing. Alternate (2026-10-10, from Nirav): Yiwei MG04254FRA1S1N is the same part as #5358. Not price-checked.</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="P32" s="17" t="inlineStr">
         <is>
-          <t>Charges AND flashes. Stock was ~35 on 10/6: order first. Backup: Jameco / DigiKey.</t>
+          <t>Charges AND flashes. Stock was ~35 on 10/6: order first. Backup: Jameco / DigiKey. Alternate (2026-10-10, from Nirav): Yiwei MG0425-UB-60-4P = equivalent of #5412; reads GND, D+, D−, V+ from its N end, like #5412. Same J3 order (1 VBUS, 2 D−, 3 D+, 4 GND, N end at pin 1) and the same meter check before gluing. Not price-checked.</t>
         </is>
       </c>
     </row>

--- a/Claude outputs/AI_Calculator_Shopping_List.xlsx
+++ b/Claude outputs/AI_Calculator_Shopping_List.xlsx
@@ -1725,7 +1725,7 @@
       </c>
       <c r="P30" s="17" t="inlineStr">
         <is>
-          <t>≈ $3 (estimate). 30 × 20 × 3 mm fits the 33.5 × 20.7 × 3.8 envelope. Generic JST leads are OFTEN REVERSED: meter it, swap pins if needed. Must have a protection board (PCM).</t>
+          <t>≈ $3 (estimate). 30 × 20 × 3 mm fits the 33.5 × 20.7 × 3.8 envelope. Generic JST leads are OFTEN REVERSED: meter it, swap pins if needed. Must have a protection board (PCM). Candidate: Taiwoo TW302030 (140 mAh, 30 × 20 × 3.0, Alibaba): CAD fit-checked 2026-10-10 (v14 + v15), it fits when placed 1 mm LEFT of the #1317 position (left edge ~1.7 mm from the corner post, top edge 0.8 mm from the lip); same tape L. Order: PCM, JST-PH 2.0 red (+) on pin 2, 50–80 mm leads, UN38.3 + MSDS (hardware/enclosure/final_assembly/battery_upgrade.md).</t>
         </is>
       </c>
     </row>

--- a/Claude outputs/AI_Calculator_Shopping_List.xlsx
+++ b/Claude outputs/AI_Calculator_Shopping_List.xlsx
@@ -214,6 +214,56 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Claude</author>
+  </authors>
+  <commentList>
+    <comment ref="A10" authorId="0" shapeId="0">
+      <text>
+        <t>2026-10-11 (Nirav): v14 was never ordered; v15-LCD was. Amount kept for history.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Claude</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0">
+      <text>
+        <t>2026-10-11 (Nirav): v14 was never ordered; v15-LCD was. Amount kept for history.</t>
+      </text>
+    </comment>
+    <comment ref="A8" authorId="0" shapeId="0">
+      <text>
+        <t>2026-10-11 (Nirav): v14 was never ordered; v15-LCD was. Amount kept for history.</t>
+      </text>
+    </comment>
+    <comment ref="B19" authorId="0" shapeId="0">
+      <text>
+        <t>2026-10-11 (Nirav): v14 was never ordered; v15-LCD was. Amount kept for history.</t>
+      </text>
+    </comment>
+    <comment ref="B20" authorId="0" shapeId="0">
+      <text>
+        <t>2026-10-11 (Nirav): v14 was never ordered; v15-LCD was. Amount kept for history.</t>
+      </text>
+    </comment>
+    <comment ref="B49" authorId="0" shapeId="0">
+      <text>
+        <t>2026-10-11 (Nirav): v14 was never ordered; v15-LCD was. Amount kept for history.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -527,6 +577,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -623,7 +674,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>…of which the JLCPCB v14 order (paid 10/8)</t>
+          <t>…of which the JLCPCB v14 order (paid 10/8) [2026-10-11: NOT ORDERED - v14 was never ordered]</t>
         </is>
       </c>
       <c r="B10" s="5">
@@ -717,6 +768,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -757,10 +809,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Updated 2026-10-08. Blue = inputs/estimates you can edit (yellow cells); black = formulas. v14 is ordered at JLCPCB (git tag v14-order). Prices: Adafruit/Seeed/Waveshare checked 2026-10-03/06; generic prices are AliExpress-level estimates; JLCPCB delivered ranges from hardware/FAB_VENDOR_COMPARISON.md.</t>
-        </is>
-      </c>
-    </row>
+          <t>Updated 2026-10-08. Blue = inputs/estimates you can edit (yellow cells); black = formulas. v14 is ordered at JLCPCB (git tag v14-order). Prices: Adafruit/Seeed/Waveshare checked 2026-10-03/06; generic prices are AliExpress-level estimates; JLCPCB delivered ranges from hardware/FAB_VENDOR_COMPARISON.md. [2026-10-11: NOT ORDERED - v14 was never ordered]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
@@ -818,7 +871,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>JLCPCB delivered, 5 PCBs with 2 assembled</t>
+          <t>JLCPCB delivered, 5 PCBs with 2 assembled [2026-10-11: NOT ORDERED - v14 was never ordered]</t>
         </is>
       </c>
       <c r="C8" s="9" t="n">
@@ -890,6 +943,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="F14" s="7" t="inlineStr">
         <is>
@@ -948,6 +1002,7 @@
         <v/>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
@@ -1034,7 +1089,7 @@
       <c r="A19" s="15" t="n"/>
       <c r="B19" s="16" t="inlineStr">
         <is>
-          <t>JLCPCB board order (v14, ordered 2026-10-08)</t>
+          <t>JLCPCB board order (v14, ordered 2026-10-08) [2026-10-11: NOT ORDERED - v14 was never ordered]</t>
         </is>
       </c>
       <c r="C19" s="15" t="n"/>
@@ -1058,7 +1113,7 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>JLCPCB v14: 5 PCBs, 2 assembled, DELIVERED (incl. DHL + US duty)</t>
+          <t>JLCPCB v14: 5 PCBs, 2 assembled, DELIVERED (incl. DHL + US duty) [2026-10-11: NOT ORDERED - v14 was never ordered]</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
@@ -2745,6 +2800,7 @@
         </is>
       </c>
     </row>
+    <row r="47"/>
     <row r="48">
       <c r="B48" s="7" t="inlineStr">
         <is>
@@ -2776,7 +2832,7 @@
     <row r="49">
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>…of which the JLCPCB order (already paid on 10/8)</t>
+          <t>…of which the JLCPCB order (already paid on 10/8) [2026-10-11: NOT ORDERED - v14 was never ordered]</t>
         </is>
       </c>
       <c r="J49" s="5">
@@ -2853,6 +2909,7 @@
         <v/>
       </c>
     </row>
+    <row r="53"/>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
@@ -2874,6 +2931,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
